--- a/Chapter_4_Analysis/Analysis_4_Factors_Poverty/Table_4_9_Objective_2_Extended.xlsx
+++ b/Chapter_4_Analysis/Analysis_4_Factors_Poverty/Table_4_9_Objective_2_Extended.xlsx
@@ -840,7 +840,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>7. Agricultural extension contact (Yes = 1)</t>
+          <t>7. Extension contact in last 12 months (Yes = 1)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
